--- a/data/Смета БХП.xlsx
+++ b/data/Смета БХП.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB29FD7B-5233-4829-98E4-3114B0446423}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="жами лойиха" sheetId="1" r:id="rId1"/>
@@ -12,7 +18,7 @@
     <sheet name="дастгох" sheetId="9" r:id="rId3"/>
     <sheet name="тухум1" sheetId="6" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="82">
   <si>
     <t>№</t>
   </si>
@@ -58,12 +64,6 @@
   </si>
   <si>
     <t>Жўжа  ташиш учун махсус транспорт автомобили</t>
-  </si>
-  <si>
-    <t>Озуқа ташиш учун махсус транспорт ҳар бири 25тн</t>
-  </si>
-  <si>
-    <t>Ишлаб чиқариладиган гўшт махсулотлари учун махсус транспорт автомабили 10 тн</t>
   </si>
   <si>
     <t>Жами</t>
@@ -606,9 +606,6 @@
     <t>Жами лойиҳалар бўйича</t>
   </si>
   <si>
-    <t>8.1</t>
-  </si>
-  <si>
     <t>8.2</t>
   </si>
   <si>
@@ -618,9 +615,6 @@
     <t>1000 тн</t>
   </si>
   <si>
-    <t>9.1</t>
-  </si>
-  <si>
     <t>9.2</t>
   </si>
   <si>
@@ -628,9 +622,6 @@
   </si>
   <si>
     <t>Озуқа заҳираси учун</t>
-  </si>
-  <si>
-    <t>5 млн доллар</t>
   </si>
   <si>
     <t>Жами кредит</t>
@@ -652,20 +643,33 @@
   </si>
   <si>
     <t>2026 йил давомида "Барака Хамкор Парранда" хусусий корхонасининг Кредитга бўлган талаб  РЕЖАСИ</t>
+  </si>
+  <si>
+    <t>Озуқа ташиш учун махсус транспорт ҳар бири 25тн дан 8 дона ва 15 тн 2 дона</t>
+  </si>
+  <si>
+    <t>8.</t>
+  </si>
+  <si>
+    <t>9.</t>
+  </si>
+  <si>
+    <t>9.1.</t>
+  </si>
+  <si>
+    <t>Генератор   (Движок)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.0\ _₽_-;\-* #,##0.0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -760,14 +764,6 @@
     </font>
     <font>
       <i/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -897,6 +893,25 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1045,7 +1060,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1061,13 +1076,10 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1085,58 +1097,58 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1147,62 +1159,62 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1212,28 +1224,22 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="18" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1242,32 +1248,41 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="28" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1284,34 +1299,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1621,14 +1636,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1638,7 +1653,7 @@
     <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="33.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1648,7 +1663,7 @@
     <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:7" ht="84" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="80" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C2" s="80"/>
       <c r="D2" s="80"/>
@@ -1665,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="78" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" s="77" t="s">
         <v>1</v>
@@ -1679,218 +1694,218 @@
       <c r="B5" s="77"/>
       <c r="C5" s="79"/>
       <c r="D5" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="27">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="35">
+      <c r="B6" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="34">
         <f>+C7+C8</f>
-        <v>21190</v>
-      </c>
-      <c r="D6" s="35">
+        <v>22455</v>
+      </c>
+      <c r="D6" s="34">
         <f>+D7+D8</f>
-        <v>6950</v>
-      </c>
-      <c r="E6" s="35">
+        <v>7780</v>
+      </c>
+      <c r="E6" s="34">
         <f t="shared" ref="E6:G6" si="0">+E7+E8</f>
-        <v>7150</v>
-      </c>
-      <c r="F6" s="35">
+        <v>7585</v>
+      </c>
+      <c r="F6" s="34">
         <f t="shared" si="0"/>
         <v>1533</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="34">
         <f t="shared" si="0"/>
         <v>5557</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="19">
+    <row r="7" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="18">
         <f>+D7+E7+F7+G7</f>
-        <v>9490</v>
-      </c>
-      <c r="D7" s="19">
+        <v>10320</v>
+      </c>
+      <c r="D7" s="18">
         <f>+броллер!J8</f>
-        <v>2400</v>
-      </c>
-      <c r="E7" s="19">
+        <v>3230</v>
+      </c>
+      <c r="E7" s="18">
         <f>+броллер!K8</f>
         <v>0</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="18">
         <f>+броллер!L8</f>
         <v>1533</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="18">
         <f>+броллер!M8</f>
         <v>5557</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="19">
+    <row r="8" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="18">
         <f>+D8+E8</f>
-        <v>11700</v>
-      </c>
-      <c r="D8" s="19">
+        <v>12135</v>
+      </c>
+      <c r="D8" s="18">
         <f>+броллер!J9</f>
         <v>4550</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="18">
         <f>+броллер!K9</f>
-        <v>7150</v>
-      </c>
-      <c r="F8" s="19">
+        <v>7585</v>
+      </c>
+      <c r="F8" s="18">
         <f>+броллер!L9</f>
         <v>0</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="18">
         <f>+броллер!M9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="12" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="21">
+    <row r="9" spans="1:7" s="11" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
         <v>2</v>
       </c>
-      <c r="B9" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="25">
+      <c r="B9" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="24">
         <f>+тухум1!I7</f>
-        <v>18030</v>
-      </c>
-      <c r="D9" s="35">
+        <v>19609</v>
+      </c>
+      <c r="D9" s="34">
         <f>+D10+D11</f>
-        <v>2600</v>
-      </c>
-      <c r="E9" s="35">
+        <v>4000</v>
+      </c>
+      <c r="E9" s="34">
         <f t="shared" ref="E9" si="1">+E10+E11</f>
-        <v>7310</v>
-      </c>
-      <c r="F9" s="35">
+        <v>7489</v>
+      </c>
+      <c r="F9" s="34">
         <f t="shared" ref="F9" si="2">+F10+F11</f>
         <v>7630</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="34">
         <f t="shared" ref="G9" si="3">+G10+G11</f>
         <v>490</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="14">
+    <row r="10" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="13">
         <f>+тухум1!I8</f>
-        <v>2890</v>
-      </c>
-      <c r="D10" s="14">
+        <v>4290</v>
+      </c>
+      <c r="D10" s="13">
         <f>+тухум1!J8</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="14">
+        <v>1400</v>
+      </c>
+      <c r="E10" s="13">
         <f>+тухум1!K8</f>
         <v>2400</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="13">
         <f>+тухум1!L8</f>
         <v>0</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="13">
         <f>+тухум1!M8</f>
         <v>490</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="14">
+    <row r="11" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="13">
         <f>+тухум1!I9</f>
-        <v>15140</v>
-      </c>
-      <c r="D11" s="14">
+        <v>15319</v>
+      </c>
+      <c r="D11" s="13">
         <f>+тухум1!J9</f>
         <v>2600</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <f>+тухум1!K9</f>
-        <v>4910</v>
-      </c>
-      <c r="F11" s="14">
+        <v>5089</v>
+      </c>
+      <c r="F11" s="13">
         <f>+тухум1!L9</f>
         <v>7630</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <f>+тухум1!M9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="12" customFormat="1" ht="42" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
+    <row r="12" spans="1:7" s="11" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+      <c r="A12" s="27">
         <v>3</v>
       </c>
-      <c r="B12" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="28">
+      <c r="B12" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="27">
         <f>+D12+E12</f>
-        <v>4610</v>
-      </c>
-      <c r="D12" s="28">
+        <v>5777.2</v>
+      </c>
+      <c r="D12" s="27">
         <f>+дастгох!G7</f>
-        <v>400</v>
-      </c>
-      <c r="E12" s="28">
+        <v>600</v>
+      </c>
+      <c r="E12" s="27">
         <f>+E13+E14</f>
-        <v>4210</v>
-      </c>
-      <c r="F12" s="28">
+        <v>5177.2</v>
+      </c>
+      <c r="F12" s="27">
         <f t="shared" ref="F12:G12" si="4">+F13+F14</f>
         <v>0</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="27">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
-      <c r="B13" s="50" t="s">
-        <v>18</v>
+      <c r="B13" s="49" t="s">
+        <v>16</v>
       </c>
       <c r="C13" s="2">
         <f>+D13+E13</f>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="D13" s="2">
         <f>+дастгох!G8</f>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E13" s="2">
         <f>+дастгох!H8</f>
@@ -1901,12 +1916,12 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
-      <c r="B14" s="50" t="s">
-        <v>19</v>
+      <c r="B14" s="49" t="s">
+        <v>17</v>
       </c>
       <c r="C14" s="2">
         <f>+D14+E14</f>
-        <v>4210</v>
+        <v>5177.2</v>
       </c>
       <c r="D14" s="2">
         <f>+дастгох!G9</f>
@@ -1914,118 +1929,120 @@
       </c>
       <c r="E14" s="2">
         <f>+дастгох!H9</f>
-        <v>4210</v>
+        <v>5177.2</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" ht="42" x14ac:dyDescent="0.25">
-      <c r="A15" s="63"/>
-      <c r="B15" s="63" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="64">
+      <c r="A15" s="60">
+        <v>4</v>
+      </c>
+      <c r="B15" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="61">
         <f>+C12+C9+C6</f>
-        <v>43830</v>
-      </c>
-      <c r="D15" s="64">
+        <v>47841.2</v>
+      </c>
+      <c r="D15" s="61">
         <f t="shared" ref="D15:G15" si="5">+D12+D9+D6</f>
-        <v>9950</v>
-      </c>
-      <c r="E15" s="64">
+        <v>12380</v>
+      </c>
+      <c r="E15" s="61">
         <f t="shared" si="5"/>
-        <v>18670</v>
-      </c>
-      <c r="F15" s="64">
+        <v>20251.2</v>
+      </c>
+      <c r="F15" s="61">
         <f t="shared" si="5"/>
         <v>9163</v>
       </c>
-      <c r="G15" s="64">
+      <c r="G15" s="61">
         <f t="shared" si="5"/>
         <v>6047</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="66"/>
-      <c r="B16" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="65">
+      <c r="A16" s="63"/>
+      <c r="B16" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="62">
         <f t="shared" ref="C16:G16" si="6">+C13+C10+C7</f>
-        <v>12780</v>
-      </c>
-      <c r="D16" s="65">
+        <v>15210</v>
+      </c>
+      <c r="D16" s="62">
         <f t="shared" si="6"/>
-        <v>2800</v>
-      </c>
-      <c r="E16" s="65">
+        <v>5230</v>
+      </c>
+      <c r="E16" s="62">
         <f t="shared" si="6"/>
         <v>2400</v>
       </c>
-      <c r="F16" s="65">
+      <c r="F16" s="62">
         <f t="shared" si="6"/>
         <v>1533</v>
       </c>
-      <c r="G16" s="65">
+      <c r="G16" s="62">
         <f t="shared" si="6"/>
         <v>6047</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="66"/>
-      <c r="B17" s="67" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="65">
+      <c r="A17" s="63"/>
+      <c r="B17" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="62">
         <f t="shared" ref="C17:G17" si="7">+C14+C11+C8</f>
-        <v>31050</v>
-      </c>
-      <c r="D17" s="65">
+        <v>32631.200000000001</v>
+      </c>
+      <c r="D17" s="62">
         <f t="shared" si="7"/>
         <v>7150</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E17" s="62">
         <f t="shared" si="7"/>
-        <v>16270</v>
-      </c>
-      <c r="F17" s="65">
+        <v>17851.2</v>
+      </c>
+      <c r="F17" s="62">
         <f t="shared" si="7"/>
         <v>7630</v>
       </c>
-      <c r="G17" s="65">
+      <c r="G17" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="A18" s="60">
+        <v>5</v>
+      </c>
+      <c r="B18" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="61">
+        <v>5000</v>
+      </c>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
-      <c r="B19" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
-      <c r="B20" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D20" s="72"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -2039,19 +2056,19 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" s="75" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="73"/>
-      <c r="B22" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="74">
-        <f>+C17+5000</f>
-        <v>36050</v>
-      </c>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
+    <row r="22" spans="1:7" s="71" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="69"/>
+      <c r="B22" s="69" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="70">
+        <f>+C17+C18</f>
+        <v>37631.199999999997</v>
+      </c>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2067,7 +2084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2092,7 +2109,7 @@
   <sheetData>
     <row r="2" spans="1:13" ht="84" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="82" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C2" s="82"/>
       <c r="D2" s="82"/>
@@ -2108,7 +2125,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K3" s="81" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L3" s="81"/>
       <c r="M3" s="81"/>
@@ -2121,21 +2138,21 @@
         <v>1</v>
       </c>
       <c r="C4" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="78" t="s">
+      <c r="E4" s="83" t="s">
         <v>13</v>
-      </c>
-      <c r="E4" s="83" t="s">
-        <v>15</v>
       </c>
       <c r="F4" s="84"/>
       <c r="G4" s="85"/>
       <c r="H4" s="78" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I4" s="78" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J4" s="77" t="s">
         <v>1</v>
@@ -2150,799 +2167,799 @@
       <c r="C5" s="79"/>
       <c r="D5" s="79"/>
       <c r="E5" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H5" s="79"/>
       <c r="I5" s="79"/>
       <c r="J5" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-    </row>
-    <row r="7" spans="1:13" s="12" customFormat="1" ht="42" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="29">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+    </row>
+    <row r="7" spans="1:13" s="11" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+      <c r="A7" s="27"/>
+      <c r="B7" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="28">
         <f>+C10+C13+C16+C19+C22+C23</f>
         <v>47</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="28">
         <f>+D10+D13+D16+D19+D22+D23+D24+D25</f>
         <v>565000</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="28">
         <f>+E10+E13+E16+E19+E22+E23+E24+E25</f>
         <v>24060</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="28">
         <f>+F10+F13+F16+F19+F22+F23+F24+F25</f>
         <v>60150</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="28">
         <f>+G10+G13+G16+G19+G22+G23+G24+G25</f>
         <v>108270</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="H7" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="28">
         <f>+I10+I13+I16+I19+I22+I24+I23+I25</f>
-        <v>21190</v>
-      </c>
-      <c r="J7" s="29">
+        <v>22455</v>
+      </c>
+      <c r="J7" s="28">
         <f>+J10+J13+J16+J19+J22+J23+J24+J25</f>
-        <v>6950</v>
-      </c>
-      <c r="K7" s="29">
+        <v>7780</v>
+      </c>
+      <c r="K7" s="28">
         <f>+K10+K13+K16+K19+K22+K23+K24+K25</f>
-        <v>7150</v>
-      </c>
-      <c r="L7" s="29">
+        <v>7585</v>
+      </c>
+      <c r="L7" s="28">
         <f>+L10+L13+L16+L19+L22+L23+L24+L25</f>
         <v>1533</v>
       </c>
-      <c r="M7" s="29">
+      <c r="M7" s="28">
         <f>+M10+M13+M16+M19+M22+M23+M24+M25</f>
         <v>5557</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="27">
+    <row r="8" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="26">
         <f t="shared" ref="I8:M9" si="0">+I11+I14+I17+I20+I26</f>
-        <v>9490</v>
-      </c>
-      <c r="J8" s="27">
+        <v>10320</v>
+      </c>
+      <c r="J8" s="26">
         <f t="shared" si="0"/>
-        <v>2400</v>
-      </c>
-      <c r="K8" s="27">
+        <v>3230</v>
+      </c>
+      <c r="K8" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="26">
         <f t="shared" si="0"/>
         <v>1533</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="26">
         <f t="shared" si="0"/>
         <v>5557</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="27">
+    <row r="9" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="26">
         <f t="shared" si="0"/>
-        <v>11700</v>
-      </c>
-      <c r="J9" s="27">
+        <v>12135</v>
+      </c>
+      <c r="J9" s="26">
         <f t="shared" si="0"/>
         <v>4550</v>
       </c>
-      <c r="K9" s="27">
+      <c r="K9" s="26">
         <f t="shared" si="0"/>
-        <v>7150</v>
-      </c>
-      <c r="L9" s="27">
+        <v>7585</v>
+      </c>
+      <c r="L9" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M9" s="27">
+      <c r="M9" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="12" customFormat="1" ht="42" x14ac:dyDescent="0.25">
-      <c r="A10" s="21">
+    <row r="10" spans="1:13" s="11" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
         <v>1</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="23">
+      <c r="B10" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="22">
         <v>7</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="22">
         <v>80000</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="23">
         <f>+D10*C10*6/1000</f>
         <v>3360</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="22">
         <f>+E10*2.5</f>
         <v>8400</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="25">
         <f>+F10*1.8</f>
         <v>15120</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="24">
         <f>+J10+K10+L10+M10</f>
-        <v>4500</v>
-      </c>
-      <c r="J10" s="25">
+        <v>4805</v>
+      </c>
+      <c r="J10" s="24">
         <f>+J11++J12</f>
-        <v>1700</v>
-      </c>
-      <c r="K10" s="25">
+        <v>1900</v>
+      </c>
+      <c r="K10" s="24">
         <f t="shared" ref="K10:M10" si="1">+K11+K12</f>
-        <v>1400</v>
-      </c>
-      <c r="L10" s="25">
+        <v>1505</v>
+      </c>
+      <c r="L10" s="24">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M10" s="24">
         <f t="shared" si="1"/>
         <v>1100</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="15" t="s">
+    <row r="11" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="19">
+      <c r="B11" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="18">
         <f>+J11+K11+L11+M11</f>
-        <v>2000</v>
-      </c>
-      <c r="J11" s="19">
-        <v>600</v>
-      </c>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19">
+        <v>2200</v>
+      </c>
+      <c r="J11" s="18">
+        <v>800</v>
+      </c>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18">
         <v>300</v>
       </c>
-      <c r="M11" s="19">
+      <c r="M11" s="18">
         <v>1100</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="15" t="s">
+    <row r="12" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="19">
+      <c r="B12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="18">
         <f t="shared" ref="I12" si="2">+J12+K12</f>
-        <v>2500</v>
-      </c>
-      <c r="J12" s="19">
+        <v>2605</v>
+      </c>
+      <c r="J12" s="18">
         <v>1100</v>
       </c>
-      <c r="K12" s="19">
-        <v>1400</v>
-      </c>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-    </row>
-    <row r="13" spans="1:13" s="12" customFormat="1" ht="42" x14ac:dyDescent="0.25">
-      <c r="A13" s="21">
+      <c r="K12" s="18">
+        <v>1505</v>
+      </c>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+    </row>
+    <row r="13" spans="1:13" s="11" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
         <v>2</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="23">
+      <c r="B13" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="22">
         <v>8</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="22">
         <v>80000</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="23">
         <f>+D13*C13*6/1000</f>
         <v>3840</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="22">
         <f>+E13*2.5</f>
         <v>9600</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="25">
         <f>+F13*1.8</f>
         <v>17280</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="24">
         <f>+J13+K13+L13+M13</f>
-        <v>5050</v>
-      </c>
-      <c r="J13" s="25">
+        <v>5400</v>
+      </c>
+      <c r="J13" s="24">
         <f>+J14+J15</f>
-        <v>1850</v>
-      </c>
-      <c r="K13" s="68">
+        <v>2080</v>
+      </c>
+      <c r="K13" s="65">
         <f t="shared" ref="K13:L13" si="3">+K14+K15</f>
-        <v>1600</v>
-      </c>
-      <c r="L13" s="68">
+        <v>1720</v>
+      </c>
+      <c r="L13" s="65">
         <f t="shared" si="3"/>
         <v>343</v>
       </c>
-      <c r="M13" s="68">
+      <c r="M13" s="65">
         <f>+M14+M15</f>
         <v>1257</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="19">
+    <row r="14" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="18">
         <f>+J14+K14+L14+M14</f>
-        <v>2200</v>
-      </c>
-      <c r="J14" s="19">
-        <v>600</v>
-      </c>
-      <c r="K14" s="19">
-        <v>0</v>
-      </c>
-      <c r="L14" s="19">
+        <v>2430</v>
+      </c>
+      <c r="J14" s="18">
+        <v>830</v>
+      </c>
+      <c r="K14" s="18">
+        <v>0</v>
+      </c>
+      <c r="L14" s="18">
         <v>343</v>
       </c>
-      <c r="M14" s="19">
+      <c r="M14" s="18">
         <v>1257</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="19">
+    <row r="15" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="18">
         <f>+J15+K15+L15+M15</f>
-        <v>2850</v>
-      </c>
-      <c r="J15" s="19">
+        <v>2970</v>
+      </c>
+      <c r="J15" s="18">
         <v>1250</v>
       </c>
-      <c r="K15" s="19">
-        <v>1600</v>
-      </c>
-      <c r="L15" s="19">
-        <v>0</v>
-      </c>
-      <c r="M15" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" s="12" customFormat="1" ht="42" x14ac:dyDescent="0.25">
-      <c r="A16" s="21">
+      <c r="K15" s="18">
+        <v>1720</v>
+      </c>
+      <c r="L15" s="18">
+        <v>0</v>
+      </c>
+      <c r="M15" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="11" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+      <c r="A16" s="20">
         <v>3</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="23">
+      <c r="B16" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="22">
         <v>7</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="22">
         <v>80000</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="23">
         <f>+D16*C16*6/1000</f>
         <v>3360</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="22">
         <f>+E16*2.5</f>
         <v>8400</v>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="25">
         <f>+F16*1.8</f>
         <v>15120</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="24">
         <f>+I17+I18</f>
-        <v>4500</v>
-      </c>
-      <c r="J16" s="68">
+        <v>4805</v>
+      </c>
+      <c r="J16" s="65">
         <f>+J17+J18</f>
-        <v>1700</v>
-      </c>
-      <c r="K16" s="68">
+        <v>1900</v>
+      </c>
+      <c r="K16" s="65">
         <f t="shared" ref="K16:M16" si="4">+K17+K18</f>
-        <v>1400</v>
-      </c>
-      <c r="L16" s="68">
+        <v>1505</v>
+      </c>
+      <c r="L16" s="65">
         <f t="shared" si="4"/>
         <v>300</v>
       </c>
-      <c r="M16" s="68">
+      <c r="M16" s="65">
         <f t="shared" si="4"/>
         <v>1100</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="19">
+      <c r="A17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="18">
         <f>+J17+K17+L17+M17</f>
-        <v>2000</v>
-      </c>
-      <c r="J17" s="19">
-        <v>600</v>
-      </c>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19">
+        <v>2200</v>
+      </c>
+      <c r="J17" s="18">
+        <v>800</v>
+      </c>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18">
         <v>300</v>
       </c>
-      <c r="M17" s="19">
+      <c r="M17" s="18">
         <v>1100</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="19">
+      <c r="A18" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="18">
         <f t="shared" ref="I18" si="5">+J18+K18</f>
-        <v>2500</v>
-      </c>
-      <c r="J18" s="19">
+        <v>2605</v>
+      </c>
+      <c r="J18" s="18">
         <v>1100</v>
       </c>
-      <c r="K18" s="19">
-        <v>1400</v>
-      </c>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
+      <c r="K18" s="18">
+        <v>1505</v>
+      </c>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
     </row>
     <row r="19" spans="1:13" ht="42" x14ac:dyDescent="0.25">
-      <c r="A19" s="21">
+      <c r="A19" s="20">
         <v>4</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="23">
+      <c r="B19" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="22">
         <v>7</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="22">
         <v>80000</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="23">
         <f>+D19*C19*6/1000</f>
         <v>3360</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="22">
         <f>+E19*2.5</f>
         <v>8400</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="25">
         <f>+F19*1.8</f>
         <v>15120</v>
       </c>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="24">
         <f>+I20+I21</f>
-        <v>4500</v>
-      </c>
-      <c r="J19" s="68">
+        <v>4805</v>
+      </c>
+      <c r="J19" s="65">
         <f>+J21+J20</f>
-        <v>1700</v>
-      </c>
-      <c r="K19" s="68">
+        <v>1900</v>
+      </c>
+      <c r="K19" s="65">
         <f t="shared" ref="K19:M19" si="6">+K21+K20</f>
-        <v>1400</v>
-      </c>
-      <c r="L19" s="68">
+        <v>1505</v>
+      </c>
+      <c r="L19" s="65">
         <f t="shared" si="6"/>
         <v>300</v>
       </c>
-      <c r="M19" s="68">
+      <c r="M19" s="65">
         <f t="shared" si="6"/>
         <v>1100</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="19">
+      <c r="A20" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="18">
         <f>+J20+K20+L20+M20</f>
-        <v>2000</v>
-      </c>
-      <c r="J20" s="19">
-        <v>600</v>
-      </c>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19">
+        <v>2200</v>
+      </c>
+      <c r="J20" s="18">
+        <v>800</v>
+      </c>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18">
         <v>300</v>
       </c>
-      <c r="M20" s="19">
+      <c r="M20" s="18">
         <v>1100</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="19">
+      <c r="A21" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="18">
         <f>+J21+K21</f>
-        <v>2500</v>
-      </c>
-      <c r="J21" s="19">
+        <v>2605</v>
+      </c>
+      <c r="J21" s="18">
         <v>1100</v>
       </c>
-      <c r="K21" s="19">
-        <v>1400</v>
-      </c>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
+      <c r="K21" s="18">
+        <v>1505</v>
+      </c>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
     </row>
     <row r="22" spans="1:13" ht="42" x14ac:dyDescent="0.25">
-      <c r="A22" s="21">
+      <c r="A22" s="20">
         <v>5</v>
       </c>
-      <c r="B22" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="23">
+      <c r="B22" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="22">
         <v>4</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="22">
         <v>80000</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="23">
         <f>+D22*C22*6/1000</f>
         <v>1920</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="22">
         <f>+E22*2.5</f>
         <v>4800</v>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="25">
         <f>+F22*1.8</f>
         <v>8640</v>
       </c>
-      <c r="H22" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="I22" s="69">
+      <c r="H22" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" s="66">
         <f>+J22+K22+L22+M22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="70"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="70"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
     </row>
     <row r="23" spans="1:13" ht="42" x14ac:dyDescent="0.25">
-      <c r="A23" s="21">
+      <c r="A23" s="20">
         <v>6</v>
       </c>
-      <c r="B23" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="23">
+      <c r="B23" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="22">
         <v>14</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="22">
         <v>25000</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="23">
         <f>+D23*C23*6/1000</f>
         <v>2100</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="22">
         <f>+E23*2.5</f>
         <v>5250</v>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="25">
         <f>+F23*1.8</f>
         <v>9450</v>
       </c>
-      <c r="H23" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="70"/>
-      <c r="K23" s="70"/>
-      <c r="L23" s="70"/>
-      <c r="M23" s="70"/>
+      <c r="H23" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" s="8"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
     </row>
     <row r="24" spans="1:13" ht="42" x14ac:dyDescent="0.25">
-      <c r="A24" s="21">
+      <c r="A24" s="20">
         <v>7</v>
       </c>
-      <c r="B24" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="23">
+      <c r="B24" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="22">
         <v>6</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="22">
         <v>80000</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="23">
         <f>+D24*C24*6/1000</f>
         <v>2880</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="22">
         <f>+E24*2.5</f>
         <v>7200</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="25">
         <f>+F24*1.8</f>
         <v>12960</v>
       </c>
-      <c r="H24" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="I24" s="69">
+      <c r="H24" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" s="66">
         <f>+J24+K24+L24+M24</f>
         <v>0</v>
       </c>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="71"/>
-      <c r="M24" s="69"/>
+      <c r="J24" s="66"/>
+      <c r="K24" s="66"/>
+      <c r="L24" s="68"/>
+      <c r="M24" s="66"/>
     </row>
     <row r="25" spans="1:13" ht="42" x14ac:dyDescent="0.25">
-      <c r="A25" s="21">
+      <c r="A25" s="20">
         <v>8</v>
       </c>
-      <c r="B25" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="23">
+      <c r="B25" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="22">
         <v>9</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="22">
         <v>60000</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="23">
         <f>+D25*C25*6/1000</f>
         <v>3240</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="22">
         <f>+E25*2.5</f>
         <v>8100</v>
       </c>
-      <c r="G25" s="26">
+      <c r="G25" s="25">
         <f>+F25*1.8</f>
         <v>14580</v>
       </c>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I25" s="24">
         <f>+I26+I27</f>
         <v>2640</v>
       </c>
-      <c r="J25" s="25">
+      <c r="J25" s="24">
         <f t="shared" ref="J25:L25" si="7">+J26+J27</f>
         <v>0</v>
       </c>
-      <c r="K25" s="25">
+      <c r="K25" s="24">
         <f>+K26+K27</f>
         <v>1350</v>
       </c>
-      <c r="L25" s="25">
+      <c r="L25" s="24">
         <f t="shared" si="7"/>
         <v>290</v>
       </c>
-      <c r="M25" s="25">
+      <c r="M25" s="24">
         <f>+M26+M27</f>
         <v>1000</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="19">
+      <c r="A26" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="18">
         <f>+J26+K26+L26+M26</f>
         <v>1290</v>
       </c>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19">
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18">
         <v>290</v>
       </c>
-      <c r="M26" s="19">
+      <c r="M26" s="18">
         <v>1000</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="19">
+      <c r="A27" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="18">
         <f t="shared" ref="I27" si="8">+J27+K27</f>
         <v>1350</v>
       </c>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19">
+      <c r="J27" s="18"/>
+      <c r="K27" s="18">
         <f>9*150</f>
         <v>1350</v>
       </c>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-    </row>
-    <row r="28" spans="1:13" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+    </row>
+    <row r="28" spans="1:13" s="7" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2963,7 +2980,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2975,15 +2992,15 @@
     <col min="3" max="3" width="13.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="84" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="82" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C2" s="82"/>
       <c r="D2" s="82"/>
@@ -2994,7 +3011,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F3" s="81" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G3" s="81"/>
       <c r="H3" s="81"/>
@@ -3007,16 +3024,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="78" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="78" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" s="78" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F4" s="78" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G4" s="77" t="s">
         <v>1</v>
@@ -3031,688 +3048,681 @@
       <c r="E5" s="79"/>
       <c r="F5" s="79"/>
       <c r="G5" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-    </row>
-    <row r="7" spans="1:8" s="12" customFormat="1" ht="42" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="29">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:8" s="11" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+      <c r="A7" s="27"/>
+      <c r="B7" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="28">
         <f>+C10+C13+C16+C19+C22+C23</f>
         <v>8</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="28">
         <f t="shared" ref="D7" si="0">+D10+D13+D16+D19+D22+D23</f>
         <v>18000</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="62">
+      <c r="F7" s="72">
         <f>+G7+H7</f>
-        <v>4610</v>
-      </c>
-      <c r="G7" s="29">
-        <f t="shared" ref="G7:H9" si="1">+G10+G13+G16+G19+G22+G25+G28+G31+G34</f>
+        <v>5777.2</v>
+      </c>
+      <c r="G7" s="28">
+        <f>+G10+G13+G16+G19+G22+G25+G28+G31</f>
+        <v>600</v>
+      </c>
+      <c r="H7" s="28">
+        <f>+H10+H13+H16+H19+H22+H25+H28+H31+H34</f>
+        <v>5177.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="73">
+        <f>+F11+F14+F17+F20+F23+F26+F29+F32</f>
+        <v>600</v>
+      </c>
+      <c r="G8" s="26">
+        <f>+G11+G14+G17+G20+G23+G26+G29+G32+G35</f>
+        <v>600</v>
+      </c>
+      <c r="H8" s="26">
+        <f>+H11+H14+H17+H20+H23+H26+H29+H32+H35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="73">
+        <f>+F12+F15+F18+F21+F24+F27+F30+F33</f>
+        <v>4795</v>
+      </c>
+      <c r="G9" s="26">
+        <f>+G12+G15+G18+G21+G24+G27+G30+G33+G36</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="26">
+        <f>+H12+H15+H18+H21+H24+H27+H30+H33+H36</f>
+        <v>5177.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>1</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="22">
+        <v>1</v>
+      </c>
+      <c r="D10" s="22">
+        <v>6000</v>
+      </c>
+      <c r="E10" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="74">
+        <f>+G10+H10</f>
+        <v>700</v>
+      </c>
+      <c r="G10" s="24">
+        <f>+G11+G12</f>
+        <v>300</v>
+      </c>
+      <c r="H10" s="24">
+        <f>+H11+H12</f>
         <v>400</v>
       </c>
-      <c r="H7" s="29">
-        <f t="shared" si="1"/>
-        <v>4210</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="15" t="s">
+    </row>
+    <row r="11" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="27">
-        <f>+F11+F14+F17+F20+F23+F26+F29+F32+F35</f>
+      <c r="B11" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="75">
+        <f>+G11+H11</f>
+        <v>300</v>
+      </c>
+      <c r="G11" s="18">
+        <v>300</v>
+      </c>
+      <c r="H11" s="18"/>
+    </row>
+    <row r="12" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="75">
+        <f>+G12+H12</f>
         <v>400</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G12" s="18"/>
+      <c r="H12" s="18">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
+        <v>2</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="22">
+        <v>1</v>
+      </c>
+      <c r="D13" s="22">
+        <v>6000</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="74">
+        <f>+F14+F15</f>
+        <v>700</v>
+      </c>
+      <c r="G13" s="24">
+        <f>+G14+G15</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="24">
+        <f>+H14+H15</f>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="75">
+        <f>+G14+H14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="18">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="75">
+        <f>+G15+H15</f>
+        <v>700</v>
+      </c>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+      <c r="A16" s="20">
+        <v>3</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="22">
+        <v>1</v>
+      </c>
+      <c r="D16" s="22">
+        <v>6000</v>
+      </c>
+      <c r="E16" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="74">
+        <f>+G16+H16</f>
+        <v>400</v>
+      </c>
+      <c r="G16" s="24">
+        <f>+G17+G18</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="24">
+        <f>+H17+H18</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="76">
+        <f t="shared" ref="F17:F18" si="1">+G17+H17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="76">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="H8" s="27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="27">
-        <f>+F12+F15+F18+F21+F24+F27+F30+F33+F36</f>
-        <v>4210</v>
-      </c>
-      <c r="G9" s="27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="27">
-        <f t="shared" si="1"/>
-        <v>4210</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="12" customFormat="1" ht="42" x14ac:dyDescent="0.25">
-      <c r="A10" s="21">
+      <c r="G18" s="18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="18">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A19" s="20">
+        <v>4</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="22">
         <v>1</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="23">
-        <v>1</v>
-      </c>
-      <c r="D10" s="23">
-        <v>6000</v>
-      </c>
-      <c r="E10" s="60" t="s">
+      <c r="D19" s="22"/>
+      <c r="E19" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="25">
-        <f>+G10+H10</f>
-        <v>700</v>
-      </c>
-      <c r="G10" s="25">
-        <f>+G11+G12</f>
+      <c r="F19" s="74">
+        <f>+G19+H19</f>
+        <v>2300</v>
+      </c>
+      <c r="G19" s="24">
+        <f>+G20+G21</f>
         <v>300</v>
       </c>
-      <c r="H10" s="25">
-        <f>+H11+H12</f>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="19">
-        <f>+G11+H11</f>
+      <c r="H19" s="24">
+        <f>+H20+H21</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="76">
+        <f t="shared" ref="F20:F21" si="2">+G20+H20</f>
         <v>300</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G20" s="18">
         <v>300</v>
       </c>
-      <c r="H11" s="19"/>
-    </row>
-    <row r="12" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="19">
-        <f>+G12+H12</f>
-        <v>400</v>
-      </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="12" customFormat="1" ht="42" x14ac:dyDescent="0.25">
-      <c r="A13" s="21">
-        <v>2</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="23">
-        <v>1</v>
-      </c>
-      <c r="D13" s="23">
-        <v>6000</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="25">
-        <f>+F14+F15</f>
-        <v>700</v>
-      </c>
-      <c r="G13" s="25">
-        <f>+G14+G15</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="25">
-        <f>+H14+H15</f>
-        <v>700</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="19">
-        <f>+G14+H14</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="19">
-        <v>0</v>
-      </c>
-      <c r="H14" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="19">
-        <f>+G15+H15</f>
-        <v>700</v>
-      </c>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="12" customFormat="1" ht="42" x14ac:dyDescent="0.25">
-      <c r="A16" s="21">
+      <c r="H20" s="18"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="76">
+        <f t="shared" si="2"/>
+        <v>2000</v>
+      </c>
+      <c r="G21" s="18">
+        <v>0</v>
+      </c>
+      <c r="H21" s="18">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A22" s="20">
+        <v>5</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="22">
+        <v>4</v>
+      </c>
+      <c r="D22" s="22"/>
+      <c r="E22" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="23">
-        <v>1</v>
-      </c>
-      <c r="D16" s="23">
-        <v>6000</v>
-      </c>
-      <c r="E16" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="F16" s="25">
-        <f>+G16+H16</f>
-        <v>400</v>
-      </c>
-      <c r="G16" s="25">
-        <f>+G17+G18</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="25">
-        <f>+H17+H18</f>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="61">
-        <f t="shared" ref="F17:F18" si="2">+G17+H17</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="61">
-        <f t="shared" si="2"/>
-        <v>400</v>
-      </c>
-      <c r="G18" s="19">
-        <v>0</v>
-      </c>
-      <c r="H18" s="19">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="42" x14ac:dyDescent="0.25">
-      <c r="A19" s="21">
-        <v>4</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="23">
-        <v>1</v>
-      </c>
-      <c r="D19" s="23"/>
-      <c r="E19" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" s="25">
-        <f>+G19+H19</f>
-        <v>600</v>
-      </c>
-      <c r="G19" s="25">
-        <f>+G20+G21</f>
-        <v>100</v>
-      </c>
-      <c r="H19" s="25">
-        <f>+H20+H21</f>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="61">
-        <f t="shared" ref="F20:F21" si="3">+G20+H20</f>
-        <v>100</v>
-      </c>
-      <c r="G20" s="19">
-        <v>100</v>
-      </c>
-      <c r="H20" s="19"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="61">
-        <f t="shared" si="3"/>
-        <v>500</v>
-      </c>
-      <c r="G21" s="19">
-        <v>0</v>
-      </c>
-      <c r="H21" s="19">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="42" x14ac:dyDescent="0.25">
-      <c r="A22" s="21">
-        <v>5</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="23">
-        <v>4</v>
-      </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="25">
+      <c r="F22" s="74">
         <f>+G22+H22</f>
         <v>400</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="24">
         <f>+G23+G24</f>
         <v>0</v>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="24">
         <f>+H23+H24</f>
         <v>400</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="61">
-        <f t="shared" ref="F23:F24" si="4">+G23+H23</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="19">
-        <v>0</v>
-      </c>
-      <c r="H23" s="19"/>
+      <c r="A23" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="76">
+        <f t="shared" ref="F23:F24" si="3">+G23+H23</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="18">
+        <v>0</v>
+      </c>
+      <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="61">
-        <f t="shared" si="4"/>
+      <c r="A24" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="76">
+        <f t="shared" si="3"/>
         <v>400</v>
       </c>
-      <c r="G24" s="19">
-        <v>0</v>
-      </c>
-      <c r="H24" s="19">
+      <c r="G24" s="18">
+        <v>0</v>
+      </c>
+      <c r="H24" s="18">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="42" x14ac:dyDescent="0.25">
-      <c r="A25" s="21">
+    <row r="25" spans="1:8" ht="63" x14ac:dyDescent="0.25">
+      <c r="A25" s="20">
         <v>6</v>
       </c>
-      <c r="B25" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="23">
-        <v>8</v>
-      </c>
-      <c r="D25" s="23"/>
-      <c r="E25" s="60" t="s">
+      <c r="B25" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="22">
+        <v>10</v>
+      </c>
+      <c r="D25" s="22"/>
+      <c r="E25" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="74">
         <f>+G25+H25</f>
-        <v>560</v>
-      </c>
-      <c r="G25" s="25">
+        <v>345</v>
+      </c>
+      <c r="G25" s="24">
         <f>+G26+G27</f>
         <v>0</v>
       </c>
-      <c r="H25" s="25">
+      <c r="H25" s="24">
         <f>+H26+H27</f>
-        <v>560</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="61">
-        <f t="shared" ref="F26:F27" si="5">+G26+H26</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
+      <c r="A26" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="76">
+        <f t="shared" ref="F26" si="4">+G26+H26</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="61">
+      <c r="A27" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="76">
+        <v>345</v>
+      </c>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="7" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="20">
+        <v>7</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="22">
+        <v>1</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="74">
+        <f>+G28+H28</f>
+        <v>350</v>
+      </c>
+      <c r="G28" s="24">
+        <f>+G29+G30</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="24">
+        <f>+H29+H30</f>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="76">
+        <f t="shared" ref="F29:F30" si="5">+G29+H29</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="76">
         <f t="shared" si="5"/>
-        <v>560</v>
-      </c>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="63" x14ac:dyDescent="0.25">
-      <c r="A28" s="21">
-        <v>7</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="23">
-        <v>10</v>
-      </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="60" t="s">
+        <v>350</v>
+      </c>
+      <c r="G30" s="18">
+        <v>0</v>
+      </c>
+      <c r="H30" s="18">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="42" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="F28" s="25">
-        <f>+G28+H28</f>
-        <v>600</v>
-      </c>
-      <c r="G28" s="25">
-        <f>+G29+G30</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="25">
-        <f>+H29+H30</f>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="61">
-        <f t="shared" ref="F29:F30" si="6">+G29+H29</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="19">
-        <v>0</v>
-      </c>
-      <c r="H29" s="19"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
+      <c r="F31" s="74">
+        <f>+G31+H31</f>
+        <v>200</v>
+      </c>
+      <c r="G31" s="24">
+        <f>+G32+G33</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="24">
+        <f>+H32+H33</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="76">
+        <f t="shared" ref="F32" si="6">+G32+H32</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="61">
-        <f t="shared" si="6"/>
-        <v>600</v>
-      </c>
-      <c r="G30" s="19">
-        <v>0</v>
-      </c>
-      <c r="H30" s="19">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A31" s="21">
-        <v>8</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="23">
-        <v>1</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="E31" s="60" t="s">
+      <c r="B33" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="76">
+        <v>200</v>
+      </c>
+      <c r="G33" s="18">
+        <v>0</v>
+      </c>
+      <c r="H33" s="18">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="F31" s="25">
-        <f>+G31+H31</f>
-        <v>350</v>
-      </c>
-      <c r="G31" s="25">
-        <f>+G32+G33</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="25">
-        <f>+H32+H33</f>
-        <v>350</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="61">
-        <f t="shared" ref="F32:F33" si="7">+G32+H32</f>
-        <v>0</v>
-      </c>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+      <c r="F34" s="74">
+        <f>+G34+H34</f>
+        <v>382.2</v>
+      </c>
+      <c r="G34" s="24">
+        <f>+G35+G36</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="24">
+        <f>+H35+H36</f>
+        <v>382.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="76">
+        <f t="shared" ref="F35" si="7">+G35+H35</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B33" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="61">
-        <f t="shared" si="7"/>
-        <v>350</v>
-      </c>
-      <c r="G33" s="19">
-        <v>0</v>
-      </c>
-      <c r="H33" s="19">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="42" x14ac:dyDescent="0.25">
-      <c r="A34" s="21">
-        <v>9</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="F34" s="25">
-        <f>+G34+H34</f>
-        <v>300</v>
-      </c>
-      <c r="G34" s="25">
-        <f>+G35+G36</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="25">
-        <f>+H35+H36</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="61">
-        <f t="shared" ref="F35:F36" si="8">+G35+H35</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="61">
-        <f t="shared" si="8"/>
-        <v>300</v>
-      </c>
-      <c r="G36" s="19">
-        <v>0</v>
-      </c>
-      <c r="H36" s="19">
-        <v>300</v>
+      <c r="B36" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="76">
+        <v>0</v>
+      </c>
+      <c r="G36" s="18">
+        <v>0</v>
+      </c>
+      <c r="H36" s="18">
+        <v>382.2</v>
       </c>
     </row>
   </sheetData>
@@ -3733,7 +3743,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3748,9 +3758,9 @@
     <col min="6" max="6" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5703125" style="33" customWidth="1"/>
-    <col min="11" max="13" width="15.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" style="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5703125" style="32" customWidth="1"/>
+    <col min="11" max="13" width="15.140625" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -3762,7 +3772,7 @@
     </row>
     <row r="2" spans="1:13" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="82" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C2" s="82"/>
       <c r="D2" s="82"/>
@@ -3779,13 +3789,13 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I3" s="1"/>
       <c r="J3"/>
-      <c r="K3" s="34" t="s">
-        <v>57</v>
+      <c r="K3" s="33" t="s">
+        <v>55</v>
       </c>
       <c r="L3"/>
       <c r="M3"/>
     </row>
-    <row r="4" spans="1:13" s="36" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" s="35" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="88" t="s">
         <v>0</v>
       </c>
@@ -3793,21 +3803,21 @@
         <v>1</v>
       </c>
       <c r="C4" s="86" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="86" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E4" s="89" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F4" s="90"/>
       <c r="G4" s="91"/>
       <c r="H4" s="86" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I4" s="86" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J4" s="88" t="s">
         <v>1</v>
@@ -3816,651 +3826,659 @@
       <c r="L4" s="88"/>
       <c r="M4" s="88"/>
     </row>
-    <row r="5" spans="1:13" s="36" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" s="35" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="86"/>
       <c r="B5" s="86"/>
       <c r="C5" s="87"/>
       <c r="D5" s="87"/>
-      <c r="E5" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="37" t="s">
-        <v>27</v>
+      <c r="E5" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>25</v>
       </c>
       <c r="H5" s="87"/>
       <c r="I5" s="87"/>
-      <c r="J5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="38" t="s">
-        <v>22</v>
+      <c r="J5" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="L5" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" s="37" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-    </row>
-    <row r="7" spans="1:13" s="36" customFormat="1" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
-      <c r="B7" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="40">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+    </row>
+    <row r="7" spans="1:13" s="35" customFormat="1" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="38"/>
+      <c r="B7" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="39">
         <f>+C10+C13+C16+C19+C22</f>
         <v>24</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="39">
         <f>+D10+D13+D16+D19+D22</f>
         <v>490000</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="39">
         <f>+E10+E13+E16+E19+E22</f>
         <v>1880</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="39">
         <f>+F10+F13+F16+F19</f>
         <v>417990</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="39">
         <f>+G10+G13+G16+G19+G22</f>
         <v>42400</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="I7" s="42">
+      <c r="I7" s="41">
         <f>+I10+I13+I16+I19+I22</f>
-        <v>18030</v>
-      </c>
-      <c r="J7" s="42">
+        <v>19609</v>
+      </c>
+      <c r="J7" s="41">
         <f>+J10+J13+J16+J19+J22</f>
-        <v>2600</v>
-      </c>
-      <c r="K7" s="42">
+        <v>4000</v>
+      </c>
+      <c r="K7" s="41">
         <f>+K10+K13+K16+K19+K22</f>
-        <v>7310</v>
-      </c>
-      <c r="L7" s="42">
+        <v>7489</v>
+      </c>
+      <c r="L7" s="41">
         <f t="shared" ref="L7:M7" si="0">+L10+L13+L16+L19+L22</f>
         <v>7630</v>
       </c>
-      <c r="M7" s="42">
+      <c r="M7" s="41">
         <f t="shared" si="0"/>
         <v>490</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="54" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="49"/>
-      <c r="B8" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="52">
+    <row r="8" spans="1:13" s="53" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="48"/>
+      <c r="B8" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="51">
         <f t="shared" ref="I8:I24" si="1">+J8+K8+L8+M8</f>
-        <v>2890</v>
-      </c>
-      <c r="J8" s="53">
+        <v>4290</v>
+      </c>
+      <c r="J8" s="52">
         <f>+J11+J14+J17+J20+J23</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="53">
+        <v>1400</v>
+      </c>
+      <c r="K8" s="52">
         <f t="shared" ref="K8:M9" si="2">+K11+K14+K17+K20+K23</f>
         <v>2400</v>
       </c>
-      <c r="L8" s="53">
+      <c r="L8" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M8" s="53">
+      <c r="M8" s="52">
         <f t="shared" si="2"/>
         <v>490</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="54" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="49"/>
-      <c r="B9" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="52">
+    <row r="9" spans="1:13" s="53" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="48"/>
+      <c r="B9" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="51">
         <f t="shared" si="1"/>
-        <v>15140</v>
-      </c>
-      <c r="J9" s="53">
+        <v>15319</v>
+      </c>
+      <c r="J9" s="52">
         <f>+J12+J15+J18+J21+J24</f>
         <v>2600</v>
       </c>
-      <c r="K9" s="53">
+      <c r="K9" s="52">
         <f t="shared" si="2"/>
-        <v>4910</v>
-      </c>
-      <c r="L9" s="53">
+        <v>5089</v>
+      </c>
+      <c r="L9" s="52">
         <f t="shared" si="2"/>
         <v>7630</v>
       </c>
-      <c r="M9" s="53">
+      <c r="M9" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="36" customFormat="1" ht="56.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="43">
+    <row r="10" spans="1:13" s="35" customFormat="1" ht="56.25" x14ac:dyDescent="0.3">
+      <c r="A10" s="42">
         <v>1</v>
       </c>
-      <c r="B10" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="43">
+      <c r="B10" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="42">
         <v>3</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="42">
         <v>150000</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="44">
         <f>450000/1000</f>
         <v>450</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="45">
         <f>139330000/1000</f>
         <v>139330</v>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="45">
         <v>11600</v>
       </c>
-      <c r="H10" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="47">
+      <c r="H10" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="46">
         <f t="shared" si="1"/>
-        <v>4450</v>
-      </c>
-      <c r="J10" s="48">
+        <v>4827.5</v>
+      </c>
+      <c r="J10" s="47">
         <f>+J11+J12</f>
-        <v>500</v>
-      </c>
-      <c r="K10" s="48">
+        <v>800</v>
+      </c>
+      <c r="K10" s="47">
         <f>+K11+K12</f>
-        <v>1700</v>
-      </c>
-      <c r="L10" s="48">
+        <v>1777.5</v>
+      </c>
+      <c r="L10" s="47">
         <f>+L11+L12</f>
         <v>2250</v>
       </c>
-      <c r="M10" s="48">
+      <c r="M10" s="47">
         <f>+M11+M12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="54" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="50" t="s">
+    <row r="11" spans="1:13" s="53" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="56"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="52">
+      <c r="B11" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="51">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="59"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="59"/>
-    </row>
-    <row r="12" spans="1:13" s="54" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="50" t="s">
+        <v>300</v>
+      </c>
+      <c r="J11" s="58">
+        <v>300</v>
+      </c>
+      <c r="K11" s="58"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="58"/>
+    </row>
+    <row r="12" spans="1:13" s="53" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="52">
+      <c r="B12" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="51">
         <f t="shared" si="1"/>
-        <v>4450</v>
-      </c>
-      <c r="J12" s="59">
+        <v>4527.5</v>
+      </c>
+      <c r="J12" s="58">
         <v>500</v>
       </c>
-      <c r="K12" s="59">
-        <v>1700</v>
-      </c>
-      <c r="L12" s="59">
+      <c r="K12" s="58">
+        <v>1777.5</v>
+      </c>
+      <c r="L12" s="58">
         <v>2250</v>
       </c>
-      <c r="M12" s="59"/>
-    </row>
-    <row r="13" spans="1:13" s="36" customFormat="1" ht="56.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="43">
+      <c r="M12" s="58"/>
+    </row>
+    <row r="13" spans="1:13" s="35" customFormat="1" ht="56.25" x14ac:dyDescent="0.3">
+      <c r="A13" s="42">
         <v>2</v>
       </c>
-      <c r="B13" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="43">
+      <c r="B13" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="42">
         <v>3</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="42">
         <v>150000</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="44">
         <f>450000/1000</f>
         <v>450</v>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="42">
         <f>139330000/1000</f>
         <v>139330</v>
       </c>
-      <c r="G13" s="46">
+      <c r="G13" s="45">
         <v>11600</v>
       </c>
-      <c r="H13" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="47">
+      <c r="H13" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="46">
         <f t="shared" si="1"/>
-        <v>4450</v>
-      </c>
-      <c r="J13" s="48">
+        <v>4827.5</v>
+      </c>
+      <c r="J13" s="47">
         <f>+J14+J15</f>
-        <v>500</v>
-      </c>
-      <c r="K13" s="48">
+        <v>800</v>
+      </c>
+      <c r="K13" s="47">
         <f>+K14+K15</f>
-        <v>1700</v>
-      </c>
-      <c r="L13" s="48">
+        <v>1777.5</v>
+      </c>
+      <c r="L13" s="47">
         <f>+L14+L15</f>
         <v>2250</v>
       </c>
-      <c r="M13" s="48">
+      <c r="M13" s="47">
         <f>+M14+M15</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="54" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="55" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="52">
+    <row r="14" spans="1:13" s="53" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="51">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="59"/>
-      <c r="K14" s="59"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="53"/>
-    </row>
-    <row r="15" spans="1:13" s="54" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="55" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="52">
+        <v>300</v>
+      </c>
+      <c r="J14" s="58">
+        <v>300</v>
+      </c>
+      <c r="K14" s="58"/>
+      <c r="L14" s="58"/>
+      <c r="M14" s="52"/>
+    </row>
+    <row r="15" spans="1:13" s="53" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="51">
         <f t="shared" si="1"/>
-        <v>4450</v>
-      </c>
-      <c r="J15" s="59">
+        <v>4527.5</v>
+      </c>
+      <c r="J15" s="58">
         <v>500</v>
       </c>
-      <c r="K15" s="59">
-        <v>1700</v>
-      </c>
-      <c r="L15" s="59">
+      <c r="K15" s="58">
+        <v>1777.5</v>
+      </c>
+      <c r="L15" s="58">
         <v>2250</v>
       </c>
-      <c r="M15" s="53"/>
-    </row>
-    <row r="16" spans="1:13" s="36" customFormat="1" ht="56.25" x14ac:dyDescent="0.3">
-      <c r="A16" s="43">
+      <c r="M15" s="52"/>
+    </row>
+    <row r="16" spans="1:13" s="35" customFormat="1" ht="56.25" x14ac:dyDescent="0.3">
+      <c r="A16" s="42">
         <v>3</v>
       </c>
-      <c r="B16" s="44" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="43">
+      <c r="B16" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="42">
         <v>5</v>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="42">
         <v>90000</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="44">
         <f>450000/1000</f>
         <v>450</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="42">
         <f>139330000/1000</f>
         <v>139330</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="45">
         <v>11600</v>
       </c>
-      <c r="H16" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" s="47">
+      <c r="H16" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="46">
         <f t="shared" si="1"/>
-        <v>4850</v>
-      </c>
-      <c r="J16" s="48">
+        <v>5250</v>
+      </c>
+      <c r="J16" s="47">
         <f>+J17+J18</f>
-        <v>800</v>
-      </c>
-      <c r="K16" s="48">
+        <v>1200</v>
+      </c>
+      <c r="K16" s="47">
         <f>+K17+K18</f>
         <v>1800</v>
       </c>
-      <c r="L16" s="48">
+      <c r="L16" s="47">
         <f>+L17+L18</f>
         <v>2250</v>
       </c>
-      <c r="M16" s="48">
+      <c r="M16" s="47">
         <f>+M17+M18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="54" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="52">
+    <row r="17" spans="1:13" s="53" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="51">
         <f t="shared" si="1"/>
+        <v>2200</v>
+      </c>
+      <c r="J17" s="58">
+        <v>400</v>
+      </c>
+      <c r="K17" s="58">
         <v>1800</v>
       </c>
-      <c r="J17" s="59"/>
-      <c r="K17" s="59">
-        <v>1800</v>
-      </c>
-      <c r="L17" s="59"/>
-      <c r="M17" s="53"/>
-    </row>
-    <row r="18" spans="1:13" s="54" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="55" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="52">
+      <c r="L17" s="58"/>
+      <c r="M17" s="52"/>
+    </row>
+    <row r="18" spans="1:13" s="53" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="51">
         <f t="shared" si="1"/>
         <v>3050</v>
       </c>
-      <c r="J18" s="59">
+      <c r="J18" s="58">
         <v>800</v>
       </c>
-      <c r="K18" s="59"/>
-      <c r="L18" s="59">
+      <c r="K18" s="58"/>
+      <c r="L18" s="58">
         <v>2250</v>
       </c>
-      <c r="M18" s="53"/>
-    </row>
-    <row r="19" spans="1:13" s="36" customFormat="1" ht="75" x14ac:dyDescent="0.3">
-      <c r="A19" s="43">
+      <c r="M18" s="52"/>
+    </row>
+    <row r="19" spans="1:13" s="35" customFormat="1" ht="75" x14ac:dyDescent="0.3">
+      <c r="A19" s="42">
         <v>4</v>
       </c>
-      <c r="B19" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="43">
+      <c r="B19" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="42">
         <v>5</v>
       </c>
-      <c r="D19" s="43">
+      <c r="D19" s="42">
         <v>90000</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="44">
         <f>450000/1000</f>
         <v>450</v>
       </c>
-      <c r="F19" s="46">
+      <c r="F19" s="45">
         <f>-G19</f>
         <v>0</v>
       </c>
-      <c r="G19" s="46">
-        <v>0</v>
-      </c>
-      <c r="H19" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="I19" s="47">
+      <c r="G19" s="45">
+        <v>0</v>
+      </c>
+      <c r="H19" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="46">
         <f t="shared" si="1"/>
-        <v>2350</v>
-      </c>
-      <c r="J19" s="48">
+        <v>2774</v>
+      </c>
+      <c r="J19" s="47">
         <f>+J20+J21</f>
+        <v>1200</v>
+      </c>
+      <c r="K19" s="47">
+        <f>+K20+K21</f>
+        <v>1574</v>
+      </c>
+      <c r="L19" s="47">
+        <f>+L20+L21</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="47">
+        <f>+M20+M21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="53" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="51">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="J20" s="18">
+        <v>400</v>
+      </c>
+      <c r="K20" s="18">
+        <v>600</v>
+      </c>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+    </row>
+    <row r="21" spans="1:13" s="53" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="51">
+        <f t="shared" si="1"/>
+        <v>1774</v>
+      </c>
+      <c r="J21" s="18">
         <v>800</v>
       </c>
-      <c r="K19" s="48">
-        <f>+K20+K21</f>
-        <v>1550</v>
-      </c>
-      <c r="L19" s="48">
-        <f>+L20+L21</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="48">
-        <f>+M20+M21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" s="54" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="52">
-        <f t="shared" si="1"/>
-        <v>600</v>
-      </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19">
-        <v>600</v>
-      </c>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-    </row>
-    <row r="21" spans="1:13" s="54" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="52">
-        <f t="shared" si="1"/>
-        <v>1750</v>
-      </c>
-      <c r="J21" s="19">
-        <v>800</v>
-      </c>
-      <c r="K21" s="19">
-        <v>950</v>
-      </c>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-    </row>
-    <row r="22" spans="1:13" s="36" customFormat="1" ht="75" x14ac:dyDescent="0.3">
-      <c r="A22" s="43">
+      <c r="K21" s="18">
+        <v>974</v>
+      </c>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+    </row>
+    <row r="22" spans="1:13" s="35" customFormat="1" ht="75" x14ac:dyDescent="0.3">
+      <c r="A22" s="42">
         <v>5</v>
       </c>
-      <c r="B22" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="43">
+      <c r="B22" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="42">
         <v>8</v>
       </c>
-      <c r="D22" s="43">
+      <c r="D22" s="42">
         <v>10000</v>
       </c>
-      <c r="E22" s="45">
+      <c r="E22" s="44">
         <f>80000/1000</f>
         <v>80</v>
       </c>
-      <c r="F22" s="46">
+      <c r="F22" s="45">
         <v>17520</v>
       </c>
-      <c r="G22" s="46">
+      <c r="G22" s="45">
         <v>7600</v>
       </c>
-      <c r="H22" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="I22" s="47">
+      <c r="H22" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="46">
         <f t="shared" si="1"/>
         <v>1930</v>
       </c>
-      <c r="J22" s="48">
+      <c r="J22" s="47">
         <f>+J23+J24</f>
         <v>0</v>
       </c>
-      <c r="K22" s="48">
+      <c r="K22" s="47">
         <f>+K23+K24</f>
         <v>560</v>
       </c>
-      <c r="L22" s="48">
+      <c r="L22" s="47">
         <f>+L23+L24</f>
         <v>880</v>
       </c>
-      <c r="M22" s="48">
+      <c r="M22" s="47">
         <f>+M23+M24</f>
         <v>490</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="54" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="52">
+    <row r="23" spans="1:13" s="53" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="54" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="51">
         <f t="shared" si="1"/>
         <v>490</v>
       </c>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="59">
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="58">
         <v>490</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="54" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="52">
+    <row r="24" spans="1:13" s="53" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="51">
         <f t="shared" si="1"/>
         <v>1440</v>
       </c>
-      <c r="J24" s="59"/>
-      <c r="K24" s="59">
+      <c r="J24" s="58"/>
+      <c r="K24" s="58">
         <v>560</v>
       </c>
-      <c r="L24" s="59">
+      <c r="L24" s="58">
         <v>880</v>
       </c>
-      <c r="M24" s="59"/>
+      <c r="M24" s="58"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
@@ -4471,11 +4489,11 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="9">
